--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120912441</v>
       </c>
       <c r="B2" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,2641 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127331299</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97326</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>859477</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7428516</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127331314</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>859703</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7428001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127331315</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>859669</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7428026</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127331330</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>859645</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7428182</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127331326</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>859451</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7428031</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127331287</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91290</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>859724</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7428004</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127331332</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>859573</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7428092</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127331331</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>859666</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7428027</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127331294</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79603</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>859495</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7428024</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127331288</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>859434</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7428190</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127331311</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>859538</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7428781</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127331312</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>859551</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7428768</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127331334</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>859485</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7427951</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127331300</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92808</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>859702</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7428406</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127331337</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98359</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>859496</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7428035</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127331333</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>859576</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7428083</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127331335</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>859493</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7427919</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127331317</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>859575</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7428091</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127331316</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>859617</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7428072</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127331338</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>353</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>859704</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7428407</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127331297</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>859721</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7428024</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127331295</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>859572</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7428088</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127331313</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>859580</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7428702</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127331325</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>859461</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7427993</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127331305</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>859435</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7428369</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127331342</v>
+      </c>
+      <c r="B28" t="n">
+        <v>12354</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>101283</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Djupsvart brunbagge</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Melandrya dubia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>859534</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7428834</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127331318</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>859584</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7428075</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3424,6 +3424,1956 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127375288</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>859567</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7427909</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127375283</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>859392</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7428524</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127375293</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>859492</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7427913</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127375262</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80021</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>859390</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7428241</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127375259</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>859540</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7427886</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127375292</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>859490</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7427925</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127375269</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97326</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>859378</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7428630</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127375281</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>859300</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7428725</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127375257</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>859381</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7428622</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127375284</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>859649</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7428008</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127375258</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>859478</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7427998</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127375276</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80153</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>859629</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7428040</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127375286</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>859748</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7428036</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127375287</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>859631</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7428039</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127375282</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>859356</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7428652</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127375279</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>859213</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7428770</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127375261</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>859630</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7428024</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127375289</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91586</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>65</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>859348</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7428673</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127375265</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97326</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>859346</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7428458</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127375274</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92808</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>859351</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7428675</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127331299</v>
       </c>
       <c r="B3" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127331314</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>127331315</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>127331287</v>
       </c>
       <c r="B8" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331294</v>
+        <v>127331288</v>
       </c>
       <c r="B11" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859495</v>
+        <v>859434</v>
       </c>
       <c r="R11" t="n">
-        <v>7428024</v>
+        <v>7428190</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331288</v>
+        <v>127331311</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859434</v>
+        <v>859538</v>
       </c>
       <c r="R12" t="n">
-        <v>7428190</v>
+        <v>7428781</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331311</v>
+        <v>127331294</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>79603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859538</v>
+        <v>859495</v>
       </c>
       <c r="R13" t="n">
-        <v>7428781</v>
+        <v>7428024</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1861,7 +1861,7 @@
         <v>127331312</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>127331300</v>
       </c>
       <c r="B16" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331337</v>
+        <v>127331333</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859496</v>
+        <v>859576</v>
       </c>
       <c r="R17" t="n">
-        <v>7428035</v>
+        <v>7428083</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2246,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331333</v>
+        <v>127331337</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>859576</v>
+        <v>859496</v>
       </c>
       <c r="R18" t="n">
-        <v>7428083</v>
+        <v>7428035</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2443,7 +2443,7 @@
         <v>127331317</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>127331316</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331295</v>
+        <v>127331325</v>
       </c>
       <c r="B24" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859572</v>
+        <v>859461</v>
       </c>
       <c r="R24" t="n">
-        <v>7428088</v>
+        <v>7427993</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2899,11 +2899,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2930,32 +2925,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331313</v>
+        <v>127331305</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>78772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859580</v>
+        <v>859435</v>
       </c>
       <c r="R25" t="n">
-        <v>7428702</v>
+        <v>7428369</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3027,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331325</v>
+        <v>127331313</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859461</v>
+        <v>859580</v>
       </c>
       <c r="R26" t="n">
-        <v>7427993</v>
+        <v>7428702</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3124,32 +3119,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331305</v>
+        <v>127331295</v>
       </c>
       <c r="B27" t="n">
-        <v>78772</v>
+        <v>56849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859435</v>
+        <v>859572</v>
       </c>
       <c r="R27" t="n">
-        <v>7428369</v>
+        <v>7428088</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3195,6 +3190,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3332,7 +3332,7 @@
         <v>127331318</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B36" t="n">
-        <v>97326</v>
+        <v>98443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R36" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>97327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R37" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4212,32 +4212,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127375257</v>
+        <v>127375284</v>
       </c>
       <c r="B38" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>859381</v>
+        <v>859649</v>
       </c>
       <c r="R38" t="n">
-        <v>7428622</v>
+        <v>7428008</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4309,32 +4309,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127375284</v>
+        <v>127375257</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>859649</v>
+        <v>859381</v>
       </c>
       <c r="R39" t="n">
-        <v>7428008</v>
+        <v>7428622</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127375276</v>
+        <v>127375286</v>
       </c>
       <c r="B41" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>859629</v>
+        <v>859748</v>
       </c>
       <c r="R41" t="n">
-        <v>7428040</v>
+        <v>7428036</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127375286</v>
+        <v>127375287</v>
       </c>
       <c r="B42" t="n">
         <v>79014</v>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>859748</v>
+        <v>859631</v>
       </c>
       <c r="R42" t="n">
-        <v>7428036</v>
+        <v>7428039</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127375287</v>
+        <v>127375276</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>859631</v>
+        <v>859629</v>
       </c>
       <c r="R43" t="n">
-        <v>7428039</v>
+        <v>7428040</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4797,7 +4797,7 @@
         <v>127375282</v>
       </c>
       <c r="B44" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>127375289</v>
       </c>
       <c r="B47" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5182,32 +5182,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375265</v>
+        <v>127375274</v>
       </c>
       <c r="B48" t="n">
-        <v>97326</v>
+        <v>92809</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>859346</v>
+        <v>859351</v>
       </c>
       <c r="R48" t="n">
-        <v>7428458</v>
+        <v>7428675</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375274</v>
+        <v>127375265</v>
       </c>
       <c r="B49" t="n">
-        <v>92808</v>
+        <v>97327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>859351</v>
+        <v>859346</v>
       </c>
       <c r="R49" t="n">
-        <v>7428675</v>
+        <v>7428458</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331288</v>
+        <v>127331294</v>
       </c>
       <c r="B11" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859434</v>
+        <v>859495</v>
       </c>
       <c r="R11" t="n">
-        <v>7428190</v>
+        <v>7428024</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331294</v>
+        <v>127331288</v>
       </c>
       <c r="B13" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859495</v>
+        <v>859434</v>
       </c>
       <c r="R13" t="n">
-        <v>7428024</v>
+        <v>7428190</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331325</v>
+        <v>127331313</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859461</v>
+        <v>859580</v>
       </c>
       <c r="R24" t="n">
-        <v>7427993</v>
+        <v>7428702</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331305</v>
+        <v>127331325</v>
       </c>
       <c r="B25" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859435</v>
+        <v>859461</v>
       </c>
       <c r="R25" t="n">
-        <v>7428369</v>
+        <v>7427993</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331313</v>
+        <v>127331305</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>78772</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859580</v>
+        <v>859435</v>
       </c>
       <c r="R26" t="n">
-        <v>7428702</v>
+        <v>7428369</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127375286</v>
+        <v>127375276</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>859748</v>
+        <v>859629</v>
       </c>
       <c r="R41" t="n">
-        <v>7428036</v>
+        <v>7428040</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127375276</v>
+        <v>127375286</v>
       </c>
       <c r="B43" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>859629</v>
+        <v>859748</v>
       </c>
       <c r="R43" t="n">
-        <v>7428040</v>
+        <v>7428036</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B46" t="n">
-        <v>80146</v>
+        <v>91587</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R46" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B47" t="n">
-        <v>91587</v>
+        <v>80146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R47" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331294</v>
+        <v>127331311</v>
       </c>
       <c r="B11" t="n">
-        <v>79603</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859495</v>
+        <v>859538</v>
       </c>
       <c r="R11" t="n">
-        <v>7428024</v>
+        <v>7428781</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331311</v>
+        <v>127331294</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>79603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859538</v>
+        <v>859495</v>
       </c>
       <c r="R12" t="n">
-        <v>7428781</v>
+        <v>7428024</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331300</v>
+        <v>127331337</v>
       </c>
       <c r="B16" t="n">
-        <v>92809</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859702</v>
+        <v>859496</v>
       </c>
       <c r="R16" t="n">
-        <v>7428406</v>
+        <v>7428035</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331333</v>
+        <v>127331300</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859576</v>
+        <v>859702</v>
       </c>
       <c r="R17" t="n">
-        <v>7428083</v>
+        <v>7428406</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2246,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331337</v>
+        <v>127331333</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>859496</v>
+        <v>859576</v>
       </c>
       <c r="R18" t="n">
-        <v>7428035</v>
+        <v>7428083</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331313</v>
+        <v>127331325</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859580</v>
+        <v>859461</v>
       </c>
       <c r="R24" t="n">
-        <v>7428702</v>
+        <v>7427993</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331325</v>
+        <v>127331295</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859461</v>
+        <v>859572</v>
       </c>
       <c r="R25" t="n">
-        <v>7427993</v>
+        <v>7428088</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -2996,6 +2996,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3119,32 +3124,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>56849</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R27" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3190,11 +3195,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3221,50 +3221,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127331342</v>
+        <v>127331318</v>
       </c>
       <c r="B28" t="n">
-        <v>12354</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101283</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>859534</v>
+        <v>859584</v>
       </c>
       <c r="R28" t="n">
-        <v>7428834</v>
+        <v>7428075</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3299,18 +3294,12 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3329,45 +3318,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331318</v>
+        <v>127331342</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>12354</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>101283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>859584</v>
+        <v>859534</v>
       </c>
       <c r="R29" t="n">
-        <v>7428075</v>
+        <v>7428834</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3402,12 +3396,18 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3426,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127375288</v>
+        <v>127375283</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>859567</v>
+        <v>859392</v>
       </c>
       <c r="R30" t="n">
-        <v>7427909</v>
+        <v>7428524</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127375283</v>
+        <v>127375288</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>859392</v>
+        <v>859567</v>
       </c>
       <c r="R31" t="n">
-        <v>7428524</v>
+        <v>7427909</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>97327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R36" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B37" t="n">
-        <v>97327</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R37" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127375276</v>
+        <v>127375286</v>
       </c>
       <c r="B41" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>859629</v>
+        <v>859748</v>
       </c>
       <c r="R41" t="n">
-        <v>7428040</v>
+        <v>7428036</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127375287</v>
+        <v>127375276</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>859631</v>
+        <v>859629</v>
       </c>
       <c r="R42" t="n">
-        <v>7428039</v>
+        <v>7428040</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127375286</v>
+        <v>127375287</v>
       </c>
       <c r="B43" t="n">
         <v>79014</v>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>859748</v>
+        <v>859631</v>
       </c>
       <c r="R43" t="n">
-        <v>7428036</v>
+        <v>7428039</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331337</v>
+        <v>127331300</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>92809</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859496</v>
+        <v>859702</v>
       </c>
       <c r="R16" t="n">
-        <v>7428035</v>
+        <v>7428406</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331300</v>
+        <v>127331333</v>
       </c>
       <c r="B17" t="n">
-        <v>92809</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859702</v>
+        <v>859576</v>
       </c>
       <c r="R17" t="n">
-        <v>7428406</v>
+        <v>7428083</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2246,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331333</v>
+        <v>127331337</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>859576</v>
+        <v>859496</v>
       </c>
       <c r="R18" t="n">
-        <v>7428083</v>
+        <v>7428035</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331325</v>
+        <v>127331305</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859461</v>
+        <v>859435</v>
       </c>
       <c r="R24" t="n">
-        <v>7427993</v>
+        <v>7428369</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331295</v>
+        <v>127331325</v>
       </c>
       <c r="B25" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859572</v>
+        <v>859461</v>
       </c>
       <c r="R25" t="n">
-        <v>7428088</v>
+        <v>7427993</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -2996,11 +2996,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3027,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331305</v>
+        <v>127331295</v>
       </c>
       <c r="B26" t="n">
-        <v>78772</v>
+        <v>56849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859435</v>
+        <v>859572</v>
       </c>
       <c r="R26" t="n">
-        <v>7428369</v>
+        <v>7428088</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3098,6 +3093,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127375283</v>
+        <v>127375288</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>859392</v>
+        <v>859567</v>
       </c>
       <c r="R30" t="n">
-        <v>7428524</v>
+        <v>7427909</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127375288</v>
+        <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>859567</v>
+        <v>859392</v>
       </c>
       <c r="R31" t="n">
-        <v>7427909</v>
+        <v>7428524</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B36" t="n">
-        <v>97327</v>
+        <v>98443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R36" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>97327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R37" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4212,32 +4212,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127375284</v>
+        <v>127375257</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>859649</v>
+        <v>859381</v>
       </c>
       <c r="R38" t="n">
-        <v>7428008</v>
+        <v>7428622</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4309,32 +4309,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127375257</v>
+        <v>127375284</v>
       </c>
       <c r="B39" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>859381</v>
+        <v>859649</v>
       </c>
       <c r="R39" t="n">
-        <v>7428622</v>
+        <v>7428008</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331311</v>
+        <v>127331288</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859538</v>
+        <v>859434</v>
       </c>
       <c r="R11" t="n">
-        <v>7428781</v>
+        <v>7428190</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331294</v>
+        <v>127331311</v>
       </c>
       <c r="B12" t="n">
-        <v>79603</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859495</v>
+        <v>859538</v>
       </c>
       <c r="R12" t="n">
-        <v>7428024</v>
+        <v>7428781</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331288</v>
+        <v>127331294</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859434</v>
+        <v>859495</v>
       </c>
       <c r="R13" t="n">
-        <v>7428190</v>
+        <v>7428024</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331300</v>
+        <v>127331337</v>
       </c>
       <c r="B16" t="n">
-        <v>92809</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859702</v>
+        <v>859496</v>
       </c>
       <c r="R16" t="n">
-        <v>7428406</v>
+        <v>7428035</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331333</v>
+        <v>127331300</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859576</v>
+        <v>859702</v>
       </c>
       <c r="R17" t="n">
-        <v>7428083</v>
+        <v>7428406</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2246,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331337</v>
+        <v>127331333</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>859496</v>
+        <v>859576</v>
       </c>
       <c r="R18" t="n">
-        <v>7428035</v>
+        <v>7428083</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331305</v>
+        <v>127331325</v>
       </c>
       <c r="B24" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859435</v>
+        <v>859461</v>
       </c>
       <c r="R24" t="n">
-        <v>7428369</v>
+        <v>7427993</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331325</v>
+        <v>127331295</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859461</v>
+        <v>859572</v>
       </c>
       <c r="R25" t="n">
-        <v>7427993</v>
+        <v>7428088</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -2996,6 +2996,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3022,32 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331295</v>
+        <v>127331305</v>
       </c>
       <c r="B26" t="n">
-        <v>56849</v>
+        <v>78772</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859572</v>
+        <v>859435</v>
       </c>
       <c r="R26" t="n">
-        <v>7428088</v>
+        <v>7428369</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3093,11 +3098,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127375288</v>
+        <v>127375283</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>859567</v>
+        <v>859392</v>
       </c>
       <c r="R30" t="n">
-        <v>7427909</v>
+        <v>7428524</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127375283</v>
+        <v>127375288</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>859392</v>
+        <v>859567</v>
       </c>
       <c r="R31" t="n">
-        <v>7428524</v>
+        <v>7427909</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>97327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R36" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B37" t="n">
-        <v>97327</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R37" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127331299</v>
       </c>
       <c r="B3" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127331314</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>127331315</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>127331330</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>127331326</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>127331287</v>
       </c>
       <c r="B8" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>127331332</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>127331331</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331288</v>
+        <v>127331311</v>
       </c>
       <c r="B11" t="n">
-        <v>79632</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859434</v>
+        <v>859538</v>
       </c>
       <c r="R11" t="n">
-        <v>7428190</v>
+        <v>7428781</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331311</v>
+        <v>127331294</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>79607</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859538</v>
+        <v>859495</v>
       </c>
       <c r="R12" t="n">
-        <v>7428781</v>
+        <v>7428024</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331294</v>
+        <v>127331288</v>
       </c>
       <c r="B13" t="n">
-        <v>79603</v>
+        <v>79636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859495</v>
+        <v>859434</v>
       </c>
       <c r="R13" t="n">
-        <v>7428024</v>
+        <v>7428190</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1861,7 +1861,7 @@
         <v>127331312</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127331334</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331337</v>
+        <v>127331300</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>92813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859496</v>
+        <v>859702</v>
       </c>
       <c r="R16" t="n">
-        <v>7428035</v>
+        <v>7428406</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331300</v>
+        <v>127331337</v>
       </c>
       <c r="B17" t="n">
-        <v>92809</v>
+        <v>98364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859702</v>
+        <v>859496</v>
       </c>
       <c r="R17" t="n">
-        <v>7428406</v>
+        <v>7428035</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2249,7 +2249,7 @@
         <v>127331333</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>127331335</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>127331317</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>127331316</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>127331338</v>
       </c>
       <c r="B22" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>127331297</v>
       </c>
       <c r="B23" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331325</v>
+        <v>127331313</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859461</v>
+        <v>859580</v>
       </c>
       <c r="R24" t="n">
-        <v>7427993</v>
+        <v>7428702</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331295</v>
+        <v>127331325</v>
       </c>
       <c r="B25" t="n">
-        <v>56849</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859572</v>
+        <v>859461</v>
       </c>
       <c r="R25" t="n">
-        <v>7428088</v>
+        <v>7427993</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -2996,11 +2996,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3030,7 +3025,7 @@
         <v>127331305</v>
       </c>
       <c r="B26" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,32 +3119,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>56853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R27" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3195,6 +3190,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3221,45 +3221,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127331318</v>
+        <v>127331342</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>12357</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>101283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>859584</v>
+        <v>859534</v>
       </c>
       <c r="R28" t="n">
-        <v>7428075</v>
+        <v>7428834</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3294,12 +3299,18 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3318,50 +3329,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331342</v>
+        <v>127331318</v>
       </c>
       <c r="B29" t="n">
-        <v>12354</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101283</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>859534</v>
+        <v>859584</v>
       </c>
       <c r="R29" t="n">
-        <v>7428834</v>
+        <v>7428075</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3396,18 +3402,12 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3426,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127375283</v>
+        <v>127375288</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>859392</v>
+        <v>859567</v>
       </c>
       <c r="R30" t="n">
-        <v>7428524</v>
+        <v>7427909</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127375288</v>
+        <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>859567</v>
+        <v>859392</v>
       </c>
       <c r="R31" t="n">
-        <v>7427909</v>
+        <v>7428524</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3623,7 +3623,7 @@
         <v>127375293</v>
       </c>
       <c r="B32" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>127375262</v>
       </c>
       <c r="B33" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>127375259</v>
       </c>
       <c r="B34" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>127375292</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B36" t="n">
-        <v>97327</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R36" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>97331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R37" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4212,32 +4212,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127375257</v>
+        <v>127375284</v>
       </c>
       <c r="B38" t="n">
-        <v>57817</v>
+        <v>98447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>859381</v>
+        <v>859649</v>
       </c>
       <c r="R38" t="n">
-        <v>7428622</v>
+        <v>7428008</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4309,32 +4309,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127375284</v>
+        <v>127375257</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>57821</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>859649</v>
+        <v>859381</v>
       </c>
       <c r="R39" t="n">
-        <v>7428008</v>
+        <v>7428622</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4409,7 +4409,7 @@
         <v>127375258</v>
       </c>
       <c r="B40" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>127375286</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>127375276</v>
       </c>
       <c r="B42" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>127375287</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>127375282</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>127375279</v>
       </c>
       <c r="B45" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>127375289</v>
       </c>
       <c r="B46" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>127375261</v>
       </c>
       <c r="B47" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>127375274</v>
       </c>
       <c r="B48" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>127375265</v>
       </c>
       <c r="B49" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -1082,32 +1082,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127331330</v>
+        <v>127331287</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>859645</v>
+        <v>859724</v>
       </c>
       <c r="R6" t="n">
-        <v>7428182</v>
+        <v>7428004</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127331326</v>
+        <v>127331330</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>859451</v>
+        <v>859645</v>
       </c>
       <c r="R7" t="n">
-        <v>7428031</v>
+        <v>7428182</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127331287</v>
+        <v>127331326</v>
       </c>
       <c r="B8" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>859724</v>
+        <v>859451</v>
       </c>
       <c r="R8" t="n">
-        <v>7428004</v>
+        <v>7428031</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331311</v>
+        <v>127331294</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>79607</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859538</v>
+        <v>859495</v>
       </c>
       <c r="R11" t="n">
-        <v>7428781</v>
+        <v>7428024</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331294</v>
+        <v>127331288</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859495</v>
+        <v>859434</v>
       </c>
       <c r="R12" t="n">
-        <v>7428024</v>
+        <v>7428190</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331288</v>
+        <v>127331311</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859434</v>
+        <v>859538</v>
       </c>
       <c r="R13" t="n">
-        <v>7428190</v>
+        <v>7428781</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2149,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331337</v>
+        <v>127331333</v>
       </c>
       <c r="B17" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859496</v>
+        <v>859576</v>
       </c>
       <c r="R17" t="n">
-        <v>7428035</v>
+        <v>7428083</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2246,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331333</v>
+        <v>127331337</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>98364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>859576</v>
+        <v>859496</v>
       </c>
       <c r="R18" t="n">
-        <v>7428083</v>
+        <v>7428035</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2440,32 +2440,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331317</v>
+        <v>127331338</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>78685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>859575</v>
+        <v>859704</v>
       </c>
       <c r="R20" t="n">
-        <v>7428091</v>
+        <v>7428407</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2537,7 +2537,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331316</v>
+        <v>127331317</v>
       </c>
       <c r="B21" t="n">
         <v>98447</v>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>859617</v>
+        <v>859575</v>
       </c>
       <c r="R21" t="n">
-        <v>7428072</v>
+        <v>7428091</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2634,32 +2634,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331338</v>
+        <v>127331316</v>
       </c>
       <c r="B22" t="n">
-        <v>78685</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>859704</v>
+        <v>859617</v>
       </c>
       <c r="R22" t="n">
-        <v>7428407</v>
+        <v>7428072</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>56853</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R24" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2899,6 +2899,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,32 +3124,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>56853</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R27" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3190,11 +3195,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3426,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127375288</v>
+        <v>127375283</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>859567</v>
+        <v>859392</v>
       </c>
       <c r="R30" t="n">
-        <v>7427909</v>
+        <v>7428524</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127375283</v>
+        <v>127375288</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>859392</v>
+        <v>859567</v>
       </c>
       <c r="R31" t="n">
-        <v>7428524</v>
+        <v>7427909</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B36" t="n">
-        <v>98447</v>
+        <v>97331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R36" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B37" t="n">
-        <v>97331</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R37" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B46" t="n">
-        <v>91591</v>
+        <v>80150</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R46" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>91591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R47" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331300</v>
+        <v>127331337</v>
       </c>
       <c r="B16" t="n">
-        <v>92813</v>
+        <v>98364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859702</v>
+        <v>859496</v>
       </c>
       <c r="R16" t="n">
-        <v>7428406</v>
+        <v>7428035</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331333</v>
+        <v>127331300</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>92813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859576</v>
+        <v>859702</v>
       </c>
       <c r="R17" t="n">
-        <v>7428083</v>
+        <v>7428406</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2246,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331337</v>
+        <v>127331333</v>
       </c>
       <c r="B18" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>859496</v>
+        <v>859576</v>
       </c>
       <c r="R18" t="n">
-        <v>7428035</v>
+        <v>7428083</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B24" t="n">
-        <v>56853</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R24" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2899,11 +2899,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,32 +3119,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>56853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R27" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3195,6 +3190,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3221,50 +3221,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127331342</v>
+        <v>127331318</v>
       </c>
       <c r="B28" t="n">
-        <v>12357</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101283</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>859534</v>
+        <v>859584</v>
       </c>
       <c r="R28" t="n">
-        <v>7428834</v>
+        <v>7428075</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3299,18 +3294,12 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3329,45 +3318,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331318</v>
+        <v>127331342</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>12357</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>101283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>859584</v>
+        <v>859534</v>
       </c>
       <c r="R29" t="n">
-        <v>7428075</v>
+        <v>7428834</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3402,12 +3396,18 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B36" t="n">
-        <v>97331</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R36" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>97331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R37" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>56853</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R24" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2899,6 +2899,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,32 +3124,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>56853</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R27" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3190,11 +3195,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3221,45 +3221,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127331318</v>
+        <v>127331342</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>12357</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>101283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>859584</v>
+        <v>859534</v>
       </c>
       <c r="R28" t="n">
-        <v>7428075</v>
+        <v>7428834</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3294,12 +3299,18 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3318,50 +3329,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331342</v>
+        <v>127331318</v>
       </c>
       <c r="B29" t="n">
-        <v>12357</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101283</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>859534</v>
+        <v>859584</v>
       </c>
       <c r="R29" t="n">
-        <v>7428834</v>
+        <v>7428075</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3396,18 +3402,12 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B36" t="n">
-        <v>98447</v>
+        <v>97331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R36" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B37" t="n">
-        <v>97331</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R37" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B46" t="n">
-        <v>80150</v>
+        <v>91591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R46" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B47" t="n">
-        <v>91591</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R47" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>127331314</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>127331315</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,32 +1082,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127331287</v>
+        <v>127331330</v>
       </c>
       <c r="B6" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>859724</v>
+        <v>859645</v>
       </c>
       <c r="R6" t="n">
-        <v>7428004</v>
+        <v>7428182</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127331330</v>
+        <v>127331326</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>859645</v>
+        <v>859451</v>
       </c>
       <c r="R7" t="n">
-        <v>7428182</v>
+        <v>7428031</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127331326</v>
+        <v>127331287</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>859451</v>
+        <v>859724</v>
       </c>
       <c r="R8" t="n">
-        <v>7428031</v>
+        <v>7428004</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331294</v>
+        <v>127331288</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859495</v>
+        <v>859434</v>
       </c>
       <c r="R11" t="n">
-        <v>7428024</v>
+        <v>7428190</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331288</v>
+        <v>127331294</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859434</v>
+        <v>859495</v>
       </c>
       <c r="R12" t="n">
-        <v>7428190</v>
+        <v>7428024</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1764,7 +1764,7 @@
         <v>127331311</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>127331312</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331337</v>
+        <v>127331300</v>
       </c>
       <c r="B16" t="n">
-        <v>98364</v>
+        <v>92813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859496</v>
+        <v>859702</v>
       </c>
       <c r="R16" t="n">
-        <v>7428035</v>
+        <v>7428406</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331300</v>
+        <v>127331333</v>
       </c>
       <c r="B17" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859702</v>
+        <v>859576</v>
       </c>
       <c r="R17" t="n">
-        <v>7428406</v>
+        <v>7428083</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2246,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331333</v>
+        <v>127331337</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>98365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>859576</v>
+        <v>859496</v>
       </c>
       <c r="R18" t="n">
-        <v>7428083</v>
+        <v>7428035</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2540,7 +2540,7 @@
         <v>127331317</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>127331316</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331295</v>
+        <v>127331325</v>
       </c>
       <c r="B24" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859572</v>
+        <v>859461</v>
       </c>
       <c r="R24" t="n">
-        <v>7428088</v>
+        <v>7427993</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2899,11 +2899,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2930,10 +2925,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331325</v>
+        <v>127331305</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,21 +2936,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859461</v>
+        <v>859435</v>
       </c>
       <c r="R25" t="n">
-        <v>7427993</v>
+        <v>7428369</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3027,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331305</v>
+        <v>127331295</v>
       </c>
       <c r="B26" t="n">
-        <v>78776</v>
+        <v>56853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859435</v>
+        <v>859572</v>
       </c>
       <c r="R26" t="n">
-        <v>7428369</v>
+        <v>7428088</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3098,6 +3093,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3127,7 +3127,7 @@
         <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>127331318</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127375283</v>
+        <v>127375288</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>859392</v>
+        <v>859567</v>
       </c>
       <c r="R30" t="n">
-        <v>7428524</v>
+        <v>7427909</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127375288</v>
+        <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>859567</v>
+        <v>859392</v>
       </c>
       <c r="R31" t="n">
-        <v>7427909</v>
+        <v>7428524</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B36" t="n">
-        <v>97331</v>
+        <v>98448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R36" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>97331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R37" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4215,7 +4215,7 @@
         <v>127375284</v>
       </c>
       <c r="B38" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127375276</v>
+        <v>127375287</v>
       </c>
       <c r="B42" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>859629</v>
+        <v>859631</v>
       </c>
       <c r="R42" t="n">
-        <v>7428040</v>
+        <v>7428039</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127375287</v>
+        <v>127375276</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>859631</v>
+        <v>859629</v>
       </c>
       <c r="R43" t="n">
-        <v>7428039</v>
+        <v>7428040</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4797,7 +4797,7 @@
         <v>127375282</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5182,32 +5182,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375274</v>
+        <v>127375265</v>
       </c>
       <c r="B48" t="n">
-        <v>92813</v>
+        <v>97331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>859351</v>
+        <v>859346</v>
       </c>
       <c r="R48" t="n">
-        <v>7428675</v>
+        <v>7428458</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375265</v>
+        <v>127375274</v>
       </c>
       <c r="B49" t="n">
-        <v>97331</v>
+        <v>92813</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>859346</v>
+        <v>859351</v>
       </c>
       <c r="R49" t="n">
-        <v>7428458</v>
+        <v>7428675</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331288</v>
+        <v>127331294</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859434</v>
+        <v>859495</v>
       </c>
       <c r="R11" t="n">
-        <v>7428190</v>
+        <v>7428024</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331294</v>
+        <v>127331288</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859495</v>
+        <v>859434</v>
       </c>
       <c r="R12" t="n">
-        <v>7428024</v>
+        <v>7428190</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331300</v>
+        <v>127331333</v>
       </c>
       <c r="B16" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859702</v>
+        <v>859576</v>
       </c>
       <c r="R16" t="n">
-        <v>7428406</v>
+        <v>7428083</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331333</v>
+        <v>127331300</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>92813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859576</v>
+        <v>859702</v>
       </c>
       <c r="R17" t="n">
-        <v>7428083</v>
+        <v>7428406</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B26" t="n">
-        <v>56853</v>
+        <v>98448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R26" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3093,11 +3093,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3124,32 +3119,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>56853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R27" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3195,6 +3190,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5182,32 +5182,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375265</v>
+        <v>127375274</v>
       </c>
       <c r="B48" t="n">
-        <v>97331</v>
+        <v>92813</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>859346</v>
+        <v>859351</v>
       </c>
       <c r="R48" t="n">
-        <v>7428458</v>
+        <v>7428675</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375274</v>
+        <v>127375265</v>
       </c>
       <c r="B49" t="n">
-        <v>92813</v>
+        <v>97331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>859351</v>
+        <v>859346</v>
       </c>
       <c r="R49" t="n">
-        <v>7428675</v>
+        <v>7428458</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127331299</v>
       </c>
       <c r="B3" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127331314</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>127331315</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>127331330</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>127331326</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>127331287</v>
       </c>
       <c r="B8" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>127331332</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>127331331</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331294</v>
+        <v>127331288</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>79638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859495</v>
+        <v>859434</v>
       </c>
       <c r="R11" t="n">
-        <v>7428024</v>
+        <v>7428190</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331288</v>
+        <v>127331311</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859434</v>
+        <v>859538</v>
       </c>
       <c r="R12" t="n">
-        <v>7428190</v>
+        <v>7428781</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331311</v>
+        <v>127331294</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>79609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859538</v>
+        <v>859495</v>
       </c>
       <c r="R13" t="n">
-        <v>7428781</v>
+        <v>7428024</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1861,7 +1861,7 @@
         <v>127331312</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127331334</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>127331333</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>127331300</v>
       </c>
       <c r="B17" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>127331337</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>127331335</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>127331338</v>
       </c>
       <c r="B20" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>127331317</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>127331316</v>
       </c>
       <c r="B22" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>127331297</v>
       </c>
       <c r="B23" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331325</v>
+        <v>127331305</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859461</v>
+        <v>859435</v>
       </c>
       <c r="R24" t="n">
-        <v>7427993</v>
+        <v>7428369</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331305</v>
+        <v>127331325</v>
       </c>
       <c r="B25" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859435</v>
+        <v>859461</v>
       </c>
       <c r="R25" t="n">
-        <v>7428369</v>
+        <v>7427993</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>56855</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R26" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3093,6 +3093,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3119,32 +3124,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>56853</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R27" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3190,11 +3195,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3332,7 +3332,7 @@
         <v>127331318</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127375288</v>
+        <v>127375283</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>859567</v>
+        <v>859392</v>
       </c>
       <c r="R30" t="n">
-        <v>7427909</v>
+        <v>7428524</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127375283</v>
+        <v>127375288</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>859392</v>
+        <v>859567</v>
       </c>
       <c r="R31" t="n">
-        <v>7428524</v>
+        <v>7427909</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3725,7 +3725,7 @@
         <v>127375262</v>
       </c>
       <c r="B33" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>127375259</v>
       </c>
       <c r="B34" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>97333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R36" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B37" t="n">
-        <v>97331</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R37" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4212,32 +4212,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127375284</v>
+        <v>127375257</v>
       </c>
       <c r="B38" t="n">
-        <v>98448</v>
+        <v>57823</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>859649</v>
+        <v>859381</v>
       </c>
       <c r="R38" t="n">
-        <v>7428008</v>
+        <v>7428622</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4309,32 +4309,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127375257</v>
+        <v>127375284</v>
       </c>
       <c r="B39" t="n">
-        <v>57821</v>
+        <v>98450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>859381</v>
+        <v>859649</v>
       </c>
       <c r="R39" t="n">
-        <v>7428622</v>
+        <v>7428008</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4409,7 +4409,7 @@
         <v>127375258</v>
       </c>
       <c r="B40" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>127375286</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>127375287</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>127375276</v>
       </c>
       <c r="B43" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>127375282</v>
       </c>
       <c r="B44" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>127375279</v>
       </c>
       <c r="B45" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B46" t="n">
-        <v>91591</v>
+        <v>80152</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R46" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>91593</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R47" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5185,7 +5185,7 @@
         <v>127375274</v>
       </c>
       <c r="B48" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>127375265</v>
       </c>
       <c r="B49" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -1082,32 +1082,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127331330</v>
+        <v>127331287</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>91297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>859645</v>
+        <v>859724</v>
       </c>
       <c r="R6" t="n">
-        <v>7428182</v>
+        <v>7428004</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127331326</v>
+        <v>127331330</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>859451</v>
+        <v>859645</v>
       </c>
       <c r="R7" t="n">
-        <v>7428031</v>
+        <v>7428182</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127331287</v>
+        <v>127331326</v>
       </c>
       <c r="B8" t="n">
-        <v>91297</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>859724</v>
+        <v>859451</v>
       </c>
       <c r="R8" t="n">
-        <v>7428004</v>
+        <v>7428031</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331311</v>
+        <v>127331294</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>79609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859538</v>
+        <v>859495</v>
       </c>
       <c r="R12" t="n">
-        <v>7428781</v>
+        <v>7428024</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331294</v>
+        <v>127331311</v>
       </c>
       <c r="B13" t="n">
-        <v>79609</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859495</v>
+        <v>859538</v>
       </c>
       <c r="R13" t="n">
-        <v>7428024</v>
+        <v>7428781</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331333</v>
+        <v>127331300</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>92815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859576</v>
+        <v>859702</v>
       </c>
       <c r="R16" t="n">
-        <v>7428083</v>
+        <v>7428406</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331300</v>
+        <v>127331333</v>
       </c>
       <c r="B17" t="n">
-        <v>92815</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859702</v>
+        <v>859576</v>
       </c>
       <c r="R17" t="n">
-        <v>7428406</v>
+        <v>7428083</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331305</v>
+        <v>127331325</v>
       </c>
       <c r="B24" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859435</v>
+        <v>859461</v>
       </c>
       <c r="R24" t="n">
-        <v>7428369</v>
+        <v>7427993</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331325</v>
+        <v>127331305</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859461</v>
+        <v>859435</v>
       </c>
       <c r="R25" t="n">
-        <v>7427993</v>
+        <v>7428369</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B26" t="n">
-        <v>56855</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R26" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3093,11 +3093,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3124,32 +3119,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>56855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R27" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3195,6 +3190,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3426,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127375283</v>
+        <v>127375288</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>859392</v>
+        <v>859567</v>
       </c>
       <c r="R30" t="n">
-        <v>7428524</v>
+        <v>7427909</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127375288</v>
+        <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>859567</v>
+        <v>859392</v>
       </c>
       <c r="R31" t="n">
-        <v>7427909</v>
+        <v>7428524</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127375287</v>
+        <v>127375276</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>80159</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>859631</v>
+        <v>859629</v>
       </c>
       <c r="R42" t="n">
-        <v>7428039</v>
+        <v>7428040</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127375276</v>
+        <v>127375287</v>
       </c>
       <c r="B43" t="n">
-        <v>80159</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>859629</v>
+        <v>859631</v>
       </c>
       <c r="R43" t="n">
-        <v>7428040</v>
+        <v>7428039</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B46" t="n">
-        <v>80152</v>
+        <v>91593</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R46" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B47" t="n">
-        <v>91593</v>
+        <v>80152</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R47" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331288</v>
+        <v>127331311</v>
       </c>
       <c r="B11" t="n">
-        <v>79638</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859434</v>
+        <v>859538</v>
       </c>
       <c r="R11" t="n">
-        <v>7428190</v>
+        <v>7428781</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331294</v>
+        <v>127331288</v>
       </c>
       <c r="B12" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859495</v>
+        <v>859434</v>
       </c>
       <c r="R12" t="n">
-        <v>7428024</v>
+        <v>7428190</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331311</v>
+        <v>127331294</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>79609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859538</v>
+        <v>859495</v>
       </c>
       <c r="R13" t="n">
-        <v>7428781</v>
+        <v>7428024</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>56855</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R26" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3093,6 +3093,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3119,32 +3124,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>56855</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R27" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3190,11 +3195,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B36" t="n">
-        <v>97333</v>
+        <v>98450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R36" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>97333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R37" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -1082,32 +1082,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127331287</v>
+        <v>127331330</v>
       </c>
       <c r="B6" t="n">
-        <v>91297</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>859724</v>
+        <v>859645</v>
       </c>
       <c r="R6" t="n">
-        <v>7428004</v>
+        <v>7428182</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127331330</v>
+        <v>127331326</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>859645</v>
+        <v>859451</v>
       </c>
       <c r="R7" t="n">
-        <v>7428182</v>
+        <v>7428031</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127331326</v>
+        <v>127331287</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>91297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>859451</v>
+        <v>859724</v>
       </c>
       <c r="R8" t="n">
-        <v>7428031</v>
+        <v>7428004</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331288</v>
+        <v>127331294</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>79609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859434</v>
+        <v>859495</v>
       </c>
       <c r="R12" t="n">
-        <v>7428190</v>
+        <v>7428024</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331294</v>
+        <v>127331288</v>
       </c>
       <c r="B13" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859495</v>
+        <v>859434</v>
       </c>
       <c r="R13" t="n">
-        <v>7428024</v>
+        <v>7428190</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B26" t="n">
-        <v>56855</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R26" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3093,11 +3093,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3124,32 +3119,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>56855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R27" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3195,6 +3190,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3221,50 +3221,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127331342</v>
+        <v>127331318</v>
       </c>
       <c r="B28" t="n">
-        <v>12357</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101283</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>859534</v>
+        <v>859584</v>
       </c>
       <c r="R28" t="n">
-        <v>7428834</v>
+        <v>7428075</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3299,18 +3294,12 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3329,45 +3318,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331318</v>
+        <v>127331342</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>12357</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>101283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>859584</v>
+        <v>859534</v>
       </c>
       <c r="R29" t="n">
-        <v>7428075</v>
+        <v>7428834</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3402,12 +3396,18 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>97333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R36" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B37" t="n">
-        <v>97333</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R37" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127375276</v>
+        <v>127375287</v>
       </c>
       <c r="B42" t="n">
-        <v>80159</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>859629</v>
+        <v>859631</v>
       </c>
       <c r="R42" t="n">
-        <v>7428040</v>
+        <v>7428039</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127375287</v>
+        <v>127375276</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>80159</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>859631</v>
+        <v>859629</v>
       </c>
       <c r="R43" t="n">
-        <v>7428039</v>
+        <v>7428040</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B46" t="n">
-        <v>91593</v>
+        <v>80152</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R46" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B47" t="n">
-        <v>80152</v>
+        <v>91593</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R47" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5182,32 +5182,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375274</v>
+        <v>127375265</v>
       </c>
       <c r="B48" t="n">
-        <v>92815</v>
+        <v>97333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>859351</v>
+        <v>859346</v>
       </c>
       <c r="R48" t="n">
-        <v>7428675</v>
+        <v>7428458</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375265</v>
+        <v>127375274</v>
       </c>
       <c r="B49" t="n">
-        <v>97333</v>
+        <v>92815</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>859346</v>
+        <v>859351</v>
       </c>
       <c r="R49" t="n">
-        <v>7428458</v>
+        <v>7428675</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127331299</v>
       </c>
       <c r="B3" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127331314</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>127331315</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>127331287</v>
       </c>
       <c r="B8" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>127331311</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>127331312</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331300</v>
+        <v>127331333</v>
       </c>
       <c r="B16" t="n">
-        <v>92815</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859702</v>
+        <v>859576</v>
       </c>
       <c r="R16" t="n">
-        <v>7428406</v>
+        <v>7428083</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331333</v>
+        <v>127331300</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859576</v>
+        <v>859702</v>
       </c>
       <c r="R17" t="n">
-        <v>7428083</v>
+        <v>7428406</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2249,7 +2249,7 @@
         <v>127331337</v>
       </c>
       <c r="B18" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>127331317</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>127331316</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331325</v>
+        <v>127331295</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859461</v>
+        <v>859572</v>
       </c>
       <c r="R24" t="n">
-        <v>7427993</v>
+        <v>7428088</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2899,6 +2899,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2925,10 +2930,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331305</v>
+        <v>127331325</v>
       </c>
       <c r="B25" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2936,21 +2941,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859435</v>
+        <v>859461</v>
       </c>
       <c r="R25" t="n">
-        <v>7428369</v>
+        <v>7427993</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3022,32 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331313</v>
+        <v>127331305</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>78778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859580</v>
+        <v>859435</v>
       </c>
       <c r="R26" t="n">
-        <v>7428702</v>
+        <v>7428369</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3119,32 +3124,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>56855</v>
+        <v>98456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R27" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3190,11 +3195,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3221,45 +3221,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127331318</v>
+        <v>127331342</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>12357</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>101283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>859584</v>
+        <v>859534</v>
       </c>
       <c r="R28" t="n">
-        <v>7428075</v>
+        <v>7428834</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3294,12 +3299,18 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3318,50 +3329,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331342</v>
+        <v>127331318</v>
       </c>
       <c r="B29" t="n">
-        <v>12357</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101283</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>859534</v>
+        <v>859584</v>
       </c>
       <c r="R29" t="n">
-        <v>7428834</v>
+        <v>7428075</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3396,18 +3402,12 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>127375269</v>
       </c>
       <c r="B36" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127375281</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4212,32 +4212,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127375257</v>
+        <v>127375284</v>
       </c>
       <c r="B38" t="n">
-        <v>57823</v>
+        <v>98456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>859381</v>
+        <v>859649</v>
       </c>
       <c r="R38" t="n">
-        <v>7428622</v>
+        <v>7428008</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4309,32 +4309,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127375284</v>
+        <v>127375257</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>859649</v>
+        <v>859381</v>
       </c>
       <c r="R39" t="n">
-        <v>7428008</v>
+        <v>7428622</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127375287</v>
+        <v>127375276</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>80159</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>859631</v>
+        <v>859629</v>
       </c>
       <c r="R42" t="n">
-        <v>7428039</v>
+        <v>7428040</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127375276</v>
+        <v>127375287</v>
       </c>
       <c r="B43" t="n">
-        <v>80159</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>859629</v>
+        <v>859631</v>
       </c>
       <c r="R43" t="n">
-        <v>7428040</v>
+        <v>7428039</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4797,7 +4797,7 @@
         <v>127375282</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B46" t="n">
-        <v>80152</v>
+        <v>91599</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R46" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B47" t="n">
-        <v>91593</v>
+        <v>80152</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R47" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5182,32 +5182,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375265</v>
+        <v>127375274</v>
       </c>
       <c r="B48" t="n">
-        <v>97333</v>
+        <v>92821</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>859346</v>
+        <v>859351</v>
       </c>
       <c r="R48" t="n">
-        <v>7428458</v>
+        <v>7428675</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375274</v>
+        <v>127375265</v>
       </c>
       <c r="B49" t="n">
-        <v>92815</v>
+        <v>97339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>859351</v>
+        <v>859346</v>
       </c>
       <c r="R49" t="n">
-        <v>7428675</v>
+        <v>7428458</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127331299</v>
       </c>
       <c r="B3" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127331314</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>127331315</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>127331330</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>127331326</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>127331287</v>
       </c>
       <c r="B8" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>127331332</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>127331331</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331311</v>
+        <v>127331288</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>79641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859538</v>
+        <v>859434</v>
       </c>
       <c r="R11" t="n">
-        <v>7428781</v>
+        <v>7428190</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331294</v>
+        <v>127331311</v>
       </c>
       <c r="B12" t="n">
-        <v>79609</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859495</v>
+        <v>859538</v>
       </c>
       <c r="R12" t="n">
-        <v>7428024</v>
+        <v>7428781</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331288</v>
+        <v>127331294</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>79612</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859434</v>
+        <v>859495</v>
       </c>
       <c r="R13" t="n">
-        <v>7428190</v>
+        <v>7428024</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1861,7 +1861,7 @@
         <v>127331312</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127331334</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331333</v>
+        <v>127331300</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>92824</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859576</v>
+        <v>859702</v>
       </c>
       <c r="R16" t="n">
-        <v>7428083</v>
+        <v>7428406</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331300</v>
+        <v>127331333</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859702</v>
+        <v>859576</v>
       </c>
       <c r="R17" t="n">
-        <v>7428406</v>
+        <v>7428083</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2249,7 +2249,7 @@
         <v>127331337</v>
       </c>
       <c r="B18" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>127331335</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>127331338</v>
       </c>
       <c r="B20" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>127331317</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>127331316</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>127331297</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331295</v>
+        <v>127331305</v>
       </c>
       <c r="B24" t="n">
-        <v>56855</v>
+        <v>78781</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859572</v>
+        <v>859435</v>
       </c>
       <c r="R24" t="n">
-        <v>7428088</v>
+        <v>7428369</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2899,11 +2899,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2933,7 +2928,7 @@
         <v>127331325</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331305</v>
+        <v>127331295</v>
       </c>
       <c r="B26" t="n">
-        <v>78778</v>
+        <v>56858</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859435</v>
+        <v>859572</v>
       </c>
       <c r="R26" t="n">
-        <v>7428369</v>
+        <v>7428088</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3098,6 +3093,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3127,7 +3127,7 @@
         <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,50 +3221,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127331342</v>
+        <v>127331318</v>
       </c>
       <c r="B28" t="n">
-        <v>12357</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101283</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>859534</v>
+        <v>859584</v>
       </c>
       <c r="R28" t="n">
-        <v>7428834</v>
+        <v>7428075</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3299,18 +3294,12 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3329,45 +3318,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331318</v>
+        <v>127331342</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>12357</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>101283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>859584</v>
+        <v>859534</v>
       </c>
       <c r="R29" t="n">
-        <v>7428075</v>
+        <v>7428834</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3402,12 +3396,18 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>127375288</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>127375262</v>
       </c>
       <c r="B33" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>127375259</v>
       </c>
       <c r="B34" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>127375269</v>
       </c>
       <c r="B36" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127375281</v>
       </c>
       <c r="B37" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4212,32 +4212,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127375284</v>
+        <v>127375257</v>
       </c>
       <c r="B38" t="n">
-        <v>98456</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>859649</v>
+        <v>859381</v>
       </c>
       <c r="R38" t="n">
-        <v>7428008</v>
+        <v>7428622</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4309,32 +4309,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127375257</v>
+        <v>127375284</v>
       </c>
       <c r="B39" t="n">
-        <v>57823</v>
+        <v>98459</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>859381</v>
+        <v>859649</v>
       </c>
       <c r="R39" t="n">
-        <v>7428622</v>
+        <v>7428008</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4409,7 +4409,7 @@
         <v>127375258</v>
       </c>
       <c r="B40" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127375286</v>
+        <v>127375276</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>80162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>859748</v>
+        <v>859629</v>
       </c>
       <c r="R41" t="n">
-        <v>7428036</v>
+        <v>7428040</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127375276</v>
+        <v>127375286</v>
       </c>
       <c r="B42" t="n">
-        <v>80159</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>859629</v>
+        <v>859748</v>
       </c>
       <c r="R42" t="n">
-        <v>7428040</v>
+        <v>7428036</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4700,7 +4700,7 @@
         <v>127375287</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>127375282</v>
       </c>
       <c r="B44" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>127375279</v>
       </c>
       <c r="B45" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B46" t="n">
-        <v>91599</v>
+        <v>80155</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R46" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B47" t="n">
-        <v>80152</v>
+        <v>91602</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R47" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5182,32 +5182,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375274</v>
+        <v>127375265</v>
       </c>
       <c r="B48" t="n">
-        <v>92821</v>
+        <v>97342</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>859351</v>
+        <v>859346</v>
       </c>
       <c r="R48" t="n">
-        <v>7428675</v>
+        <v>7428458</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375265</v>
+        <v>127375274</v>
       </c>
       <c r="B49" t="n">
-        <v>97339</v>
+        <v>92824</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>859346</v>
+        <v>859351</v>
       </c>
       <c r="R49" t="n">
-        <v>7428458</v>
+        <v>7428675</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127331299</v>
       </c>
       <c r="B3" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127331314</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>127331315</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>127331330</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>127331326</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>127331287</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>127331332</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>127331331</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>127331288</v>
       </c>
       <c r="B11" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331311</v>
+        <v>127331294</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>79618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859538</v>
+        <v>859495</v>
       </c>
       <c r="R12" t="n">
-        <v>7428781</v>
+        <v>7428024</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331294</v>
+        <v>127331311</v>
       </c>
       <c r="B13" t="n">
-        <v>79612</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859495</v>
+        <v>859538</v>
       </c>
       <c r="R13" t="n">
-        <v>7428024</v>
+        <v>7428781</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1861,7 +1861,7 @@
         <v>127331312</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127331334</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>127331300</v>
       </c>
       <c r="B16" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331333</v>
+        <v>127331337</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>98384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859576</v>
+        <v>859496</v>
       </c>
       <c r="R17" t="n">
-        <v>7428083</v>
+        <v>7428035</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2246,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331337</v>
+        <v>127331333</v>
       </c>
       <c r="B18" t="n">
-        <v>98376</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>859496</v>
+        <v>859576</v>
       </c>
       <c r="R18" t="n">
-        <v>7428035</v>
+        <v>7428083</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2346,7 +2346,7 @@
         <v>127331335</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,32 +2440,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331338</v>
+        <v>127331317</v>
       </c>
       <c r="B20" t="n">
-        <v>78690</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>859704</v>
+        <v>859575</v>
       </c>
       <c r="R20" t="n">
-        <v>7428407</v>
+        <v>7428091</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331317</v>
+        <v>127331316</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>859575</v>
+        <v>859617</v>
       </c>
       <c r="R21" t="n">
-        <v>7428091</v>
+        <v>7428072</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2634,32 +2634,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331316</v>
+        <v>127331338</v>
       </c>
       <c r="B22" t="n">
-        <v>98459</v>
+        <v>78696</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>859617</v>
+        <v>859704</v>
       </c>
       <c r="R22" t="n">
-        <v>7428072</v>
+        <v>7428407</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2734,7 +2734,7 @@
         <v>127331297</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331305</v>
+        <v>127331325</v>
       </c>
       <c r="B24" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859435</v>
+        <v>859461</v>
       </c>
       <c r="R24" t="n">
-        <v>7428369</v>
+        <v>7427993</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331325</v>
+        <v>127331305</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>78787</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859461</v>
+        <v>859435</v>
       </c>
       <c r="R25" t="n">
-        <v>7427993</v>
+        <v>7428369</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3025,7 +3025,7 @@
         <v>127331295</v>
       </c>
       <c r="B26" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,45 +3221,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127331318</v>
+        <v>127331342</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>12357</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>101283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>859584</v>
+        <v>859534</v>
       </c>
       <c r="R28" t="n">
-        <v>7428075</v>
+        <v>7428834</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3294,12 +3299,18 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3318,50 +3329,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331342</v>
+        <v>127331318</v>
       </c>
       <c r="B29" t="n">
-        <v>12357</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101283</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>859534</v>
+        <v>859584</v>
       </c>
       <c r="R29" t="n">
-        <v>7428834</v>
+        <v>7428075</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3396,18 +3402,12 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>127375288</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>127375262</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>127375259</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B36" t="n">
-        <v>97342</v>
+        <v>98467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R36" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B37" t="n">
-        <v>98459</v>
+        <v>97350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R37" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4212,32 +4212,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127375257</v>
+        <v>127375284</v>
       </c>
       <c r="B38" t="n">
-        <v>57826</v>
+        <v>98467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>859381</v>
+        <v>859649</v>
       </c>
       <c r="R38" t="n">
-        <v>7428622</v>
+        <v>7428008</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4309,32 +4309,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127375284</v>
+        <v>127375257</v>
       </c>
       <c r="B39" t="n">
-        <v>98459</v>
+        <v>57832</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>859649</v>
+        <v>859381</v>
       </c>
       <c r="R39" t="n">
-        <v>7428008</v>
+        <v>7428622</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4409,7 +4409,7 @@
         <v>127375258</v>
       </c>
       <c r="B40" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>127375276</v>
       </c>
       <c r="B41" t="n">
-        <v>80162</v>
+        <v>80168</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>127375286</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>127375287</v>
       </c>
       <c r="B43" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>127375282</v>
       </c>
       <c r="B44" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>127375279</v>
       </c>
       <c r="B45" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B46" t="n">
-        <v>80155</v>
+        <v>91610</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R46" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B47" t="n">
-        <v>91602</v>
+        <v>80161</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R47" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5182,32 +5182,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375265</v>
+        <v>127375274</v>
       </c>
       <c r="B48" t="n">
-        <v>97342</v>
+        <v>92832</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>859346</v>
+        <v>859351</v>
       </c>
       <c r="R48" t="n">
-        <v>7428458</v>
+        <v>7428675</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375274</v>
+        <v>127375265</v>
       </c>
       <c r="B49" t="n">
-        <v>92824</v>
+        <v>97350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>859351</v>
+        <v>859346</v>
       </c>
       <c r="R49" t="n">
-        <v>7428675</v>
+        <v>7428458</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127331299</v>
       </c>
       <c r="B3" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127331314</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>127331315</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>127331287</v>
       </c>
       <c r="B8" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331294</v>
+        <v>127331311</v>
       </c>
       <c r="B12" t="n">
-        <v>79618</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859495</v>
+        <v>859538</v>
       </c>
       <c r="R12" t="n">
-        <v>7428024</v>
+        <v>7428781</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331311</v>
+        <v>127331294</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>79618</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859538</v>
+        <v>859495</v>
       </c>
       <c r="R13" t="n">
-        <v>7428781</v>
+        <v>7428024</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1861,7 +1861,7 @@
         <v>127331312</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331300</v>
+        <v>127331333</v>
       </c>
       <c r="B16" t="n">
-        <v>92832</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859702</v>
+        <v>859576</v>
       </c>
       <c r="R16" t="n">
-        <v>7428406</v>
+        <v>7428083</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331337</v>
+        <v>127331300</v>
       </c>
       <c r="B17" t="n">
-        <v>98384</v>
+        <v>92833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859496</v>
+        <v>859702</v>
       </c>
       <c r="R17" t="n">
-        <v>7428035</v>
+        <v>7428406</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2246,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331333</v>
+        <v>127331337</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>98385</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>859576</v>
+        <v>859496</v>
       </c>
       <c r="R18" t="n">
-        <v>7428083</v>
+        <v>7428035</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2440,32 +2440,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331317</v>
+        <v>127331338</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>78696</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>859575</v>
+        <v>859704</v>
       </c>
       <c r="R20" t="n">
-        <v>7428091</v>
+        <v>7428407</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331316</v>
+        <v>127331317</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>859617</v>
+        <v>859575</v>
       </c>
       <c r="R21" t="n">
-        <v>7428072</v>
+        <v>7428091</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2634,32 +2634,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331338</v>
+        <v>127331316</v>
       </c>
       <c r="B22" t="n">
-        <v>78696</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>859704</v>
+        <v>859617</v>
       </c>
       <c r="R22" t="n">
-        <v>7428407</v>
+        <v>7428072</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331325</v>
+        <v>127331313</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859461</v>
+        <v>859580</v>
       </c>
       <c r="R24" t="n">
-        <v>7427993</v>
+        <v>7428702</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331305</v>
+        <v>127331325</v>
       </c>
       <c r="B25" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859435</v>
+        <v>859461</v>
       </c>
       <c r="R25" t="n">
-        <v>7428369</v>
+        <v>7427993</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331295</v>
+        <v>127331305</v>
       </c>
       <c r="B26" t="n">
-        <v>56864</v>
+        <v>78787</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859572</v>
+        <v>859435</v>
       </c>
       <c r="R26" t="n">
-        <v>7428088</v>
+        <v>7428369</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3093,11 +3093,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3124,32 +3119,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>56864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R27" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3195,6 +3190,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3332,7 +3332,7 @@
         <v>127331318</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>127375281</v>
       </c>
       <c r="B36" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127375269</v>
       </c>
       <c r="B37" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4212,32 +4212,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127375284</v>
+        <v>127375257</v>
       </c>
       <c r="B38" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>859649</v>
+        <v>859381</v>
       </c>
       <c r="R38" t="n">
-        <v>7428008</v>
+        <v>7428622</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4309,32 +4309,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127375257</v>
+        <v>127375284</v>
       </c>
       <c r="B39" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>859381</v>
+        <v>859649</v>
       </c>
       <c r="R39" t="n">
-        <v>7428622</v>
+        <v>7428008</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4797,7 +4797,7 @@
         <v>127375282</v>
       </c>
       <c r="B44" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B46" t="n">
-        <v>91610</v>
+        <v>80161</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R46" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B47" t="n">
-        <v>80161</v>
+        <v>91611</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R47" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5185,7 +5185,7 @@
         <v>127375274</v>
       </c>
       <c r="B48" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>127375265</v>
       </c>
       <c r="B49" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -1082,7 +1082,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127331330</v>
+        <v>127331326</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>859645</v>
+        <v>859451</v>
       </c>
       <c r="R6" t="n">
-        <v>7428182</v>
+        <v>7428031</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127331326</v>
+        <v>127331330</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>859451</v>
+        <v>859645</v>
       </c>
       <c r="R7" t="n">
-        <v>7428031</v>
+        <v>7428182</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331288</v>
+        <v>127331294</v>
       </c>
       <c r="B11" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859434</v>
+        <v>859495</v>
       </c>
       <c r="R11" t="n">
-        <v>7428190</v>
+        <v>7428024</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331311</v>
+        <v>127331288</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>79647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859538</v>
+        <v>859434</v>
       </c>
       <c r="R12" t="n">
-        <v>7428781</v>
+        <v>7428190</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331294</v>
+        <v>127331311</v>
       </c>
       <c r="B13" t="n">
-        <v>79618</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859495</v>
+        <v>859538</v>
       </c>
       <c r="R13" t="n">
-        <v>7428024</v>
+        <v>7428781</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331333</v>
+        <v>127331300</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>92833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859576</v>
+        <v>859702</v>
       </c>
       <c r="R16" t="n">
-        <v>7428083</v>
+        <v>7428406</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331300</v>
+        <v>127331333</v>
       </c>
       <c r="B17" t="n">
-        <v>92833</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859702</v>
+        <v>859576</v>
       </c>
       <c r="R17" t="n">
-        <v>7428406</v>
+        <v>7428083</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2537,7 +2537,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331317</v>
+        <v>127331316</v>
       </c>
       <c r="B21" t="n">
         <v>98468</v>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>859575</v>
+        <v>859617</v>
       </c>
       <c r="R21" t="n">
-        <v>7428091</v>
+        <v>7428072</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2634,7 +2634,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331316</v>
+        <v>127331317</v>
       </c>
       <c r="B22" t="n">
         <v>98468</v>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>859617</v>
+        <v>859575</v>
       </c>
       <c r="R22" t="n">
-        <v>7428072</v>
+        <v>7428091</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>56864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R24" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2899,6 +2899,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,32 +3124,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>56864</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R27" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3190,11 +3195,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B46" t="n">
-        <v>80161</v>
+        <v>91611</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R46" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B47" t="n">
-        <v>91611</v>
+        <v>80161</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R47" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127331299</v>
       </c>
       <c r="B3" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127331314</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>127331315</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127331326</v>
+        <v>127331330</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>859451</v>
+        <v>859645</v>
       </c>
       <c r="R6" t="n">
-        <v>7428031</v>
+        <v>7428182</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127331330</v>
+        <v>127331326</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>859645</v>
+        <v>859451</v>
       </c>
       <c r="R7" t="n">
-        <v>7428182</v>
+        <v>7428031</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1279,7 +1279,7 @@
         <v>127331287</v>
       </c>
       <c r="B8" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331294</v>
+        <v>127331311</v>
       </c>
       <c r="B11" t="n">
-        <v>79618</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859495</v>
+        <v>859538</v>
       </c>
       <c r="R11" t="n">
-        <v>7428024</v>
+        <v>7428781</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331311</v>
+        <v>127331294</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>79618</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859538</v>
+        <v>859495</v>
       </c>
       <c r="R13" t="n">
-        <v>7428781</v>
+        <v>7428024</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1861,7 +1861,7 @@
         <v>127331312</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>127331300</v>
       </c>
       <c r="B16" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>127331337</v>
       </c>
       <c r="B18" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331316</v>
+        <v>127331317</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>859617</v>
+        <v>859575</v>
       </c>
       <c r="R21" t="n">
-        <v>7428072</v>
+        <v>7428091</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331317</v>
+        <v>127331316</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>859575</v>
+        <v>859617</v>
       </c>
       <c r="R22" t="n">
-        <v>7428091</v>
+        <v>7428072</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B24" t="n">
-        <v>56864</v>
+        <v>98469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R24" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2899,11 +2899,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,32 +3119,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331313</v>
+        <v>127331295</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>56864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859580</v>
+        <v>859572</v>
       </c>
       <c r="R27" t="n">
-        <v>7428702</v>
+        <v>7428088</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3195,6 +3190,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3332,7 +3332,7 @@
         <v>127331318</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>127375281</v>
       </c>
       <c r="B36" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127375269</v>
       </c>
       <c r="B37" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>127375284</v>
       </c>
       <c r="B39" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127375276</v>
+        <v>127375286</v>
       </c>
       <c r="B41" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>859629</v>
+        <v>859748</v>
       </c>
       <c r="R41" t="n">
-        <v>7428040</v>
+        <v>7428036</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127375286</v>
+        <v>127375287</v>
       </c>
       <c r="B42" t="n">
         <v>79029</v>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>859748</v>
+        <v>859631</v>
       </c>
       <c r="R42" t="n">
-        <v>7428036</v>
+        <v>7428039</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127375287</v>
+        <v>127375276</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>859631</v>
+        <v>859629</v>
       </c>
       <c r="R43" t="n">
-        <v>7428039</v>
+        <v>7428040</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4797,7 +4797,7 @@
         <v>127375282</v>
       </c>
       <c r="B44" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>127375289</v>
       </c>
       <c r="B46" t="n">
-        <v>91611</v>
+        <v>91612</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>127375274</v>
       </c>
       <c r="B48" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>127375265</v>
       </c>
       <c r="B49" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127331299</v>
       </c>
       <c r="B3" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127331314</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>127331315</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,32 +1082,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127331330</v>
+        <v>127331287</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>91317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>859645</v>
+        <v>859724</v>
       </c>
       <c r="R6" t="n">
-        <v>7428182</v>
+        <v>7428004</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127331326</v>
+        <v>127331330</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>859451</v>
+        <v>859645</v>
       </c>
       <c r="R7" t="n">
-        <v>7428031</v>
+        <v>7428182</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127331287</v>
+        <v>127331326</v>
       </c>
       <c r="B8" t="n">
-        <v>91316</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>859724</v>
+        <v>859451</v>
       </c>
       <c r="R8" t="n">
-        <v>7428004</v>
+        <v>7428031</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1570,7 +1570,7 @@
         <v>127331311</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127331288</v>
+        <v>127331294</v>
       </c>
       <c r="B12" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>859434</v>
+        <v>859495</v>
       </c>
       <c r="R12" t="n">
-        <v>7428190</v>
+        <v>7428024</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127331294</v>
+        <v>127331288</v>
       </c>
       <c r="B13" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859495</v>
+        <v>859434</v>
       </c>
       <c r="R13" t="n">
-        <v>7428024</v>
+        <v>7428190</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1861,7 +1861,7 @@
         <v>127331312</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>127331300</v>
       </c>
       <c r="B16" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>127331337</v>
       </c>
       <c r="B18" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>127331317</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>127331316</v>
       </c>
       <c r="B22" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2828,32 +2828,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331313</v>
+        <v>127331325</v>
       </c>
       <c r="B24" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>859580</v>
+        <v>859461</v>
       </c>
       <c r="R24" t="n">
-        <v>7428702</v>
+        <v>7427993</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127331325</v>
+        <v>127331305</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>859461</v>
+        <v>859435</v>
       </c>
       <c r="R25" t="n">
-        <v>7427993</v>
+        <v>7428369</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331305</v>
+        <v>127331295</v>
       </c>
       <c r="B26" t="n">
-        <v>78787</v>
+        <v>56864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>859435</v>
+        <v>859572</v>
       </c>
       <c r="R26" t="n">
-        <v>7428369</v>
+        <v>7428088</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3093,6 +3093,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3119,32 +3124,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331295</v>
+        <v>127331313</v>
       </c>
       <c r="B27" t="n">
-        <v>56864</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>859572</v>
+        <v>859580</v>
       </c>
       <c r="R27" t="n">
-        <v>7428088</v>
+        <v>7428702</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3190,11 +3195,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3221,50 +3221,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127331342</v>
+        <v>127331318</v>
       </c>
       <c r="B28" t="n">
-        <v>12357</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101283</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>859534</v>
+        <v>859584</v>
       </c>
       <c r="R28" t="n">
-        <v>7428834</v>
+        <v>7428075</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3299,18 +3294,12 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3329,45 +3318,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331318</v>
+        <v>127331342</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>12357</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>101283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>859584</v>
+        <v>859534</v>
       </c>
       <c r="R29" t="n">
-        <v>7428075</v>
+        <v>7428834</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3402,12 +3396,18 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Kläckhål 3 X 4 mm med svartfärgad larvgång i björkhögstubbe med fnösktickor. Bilder granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>127375283</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>127375281</v>
       </c>
       <c r="B36" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>127375269</v>
       </c>
       <c r="B37" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>127375284</v>
       </c>
       <c r="B39" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127375286</v>
+        <v>127375276</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>859748</v>
+        <v>859629</v>
       </c>
       <c r="R41" t="n">
-        <v>7428036</v>
+        <v>7428040</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127375287</v>
+        <v>127375286</v>
       </c>
       <c r="B42" t="n">
         <v>79029</v>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>859631</v>
+        <v>859748</v>
       </c>
       <c r="R42" t="n">
-        <v>7428039</v>
+        <v>7428036</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127375276</v>
+        <v>127375287</v>
       </c>
       <c r="B43" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>859629</v>
+        <v>859631</v>
       </c>
       <c r="R43" t="n">
-        <v>7428040</v>
+        <v>7428039</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4797,7 +4797,7 @@
         <v>127375282</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B46" t="n">
-        <v>91612</v>
+        <v>80161</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R46" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B47" t="n">
-        <v>80161</v>
+        <v>91613</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R47" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5182,32 +5182,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375274</v>
+        <v>127375265</v>
       </c>
       <c r="B48" t="n">
-        <v>92834</v>
+        <v>97353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>859351</v>
+        <v>859346</v>
       </c>
       <c r="R48" t="n">
-        <v>7428675</v>
+        <v>7428458</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375265</v>
+        <v>127375274</v>
       </c>
       <c r="B49" t="n">
-        <v>97352</v>
+        <v>92835</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>859346</v>
+        <v>859351</v>
       </c>
       <c r="R49" t="n">
-        <v>7428458</v>
+        <v>7428675</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -3426,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127375288</v>
+        <v>127375283</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>859567</v>
+        <v>859392</v>
       </c>
       <c r="R30" t="n">
-        <v>7427909</v>
+        <v>7428524</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127375283</v>
+        <v>127375288</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>859392</v>
+        <v>859567</v>
       </c>
       <c r="R31" t="n">
-        <v>7428524</v>
+        <v>7427909</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127375281</v>
+        <v>127375269</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>97353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>859300</v>
+        <v>859378</v>
       </c>
       <c r="R36" t="n">
-        <v>7428725</v>
+        <v>7428630</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127375269</v>
+        <v>127375281</v>
       </c>
       <c r="B37" t="n">
-        <v>97353</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>859378</v>
+        <v>859300</v>
       </c>
       <c r="R37" t="n">
-        <v>7428630</v>
+        <v>7428725</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127375276</v>
+        <v>127375286</v>
       </c>
       <c r="B41" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>859629</v>
+        <v>859748</v>
       </c>
       <c r="R41" t="n">
-        <v>7428040</v>
+        <v>7428036</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127375286</v>
+        <v>127375276</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>859748</v>
+        <v>859629</v>
       </c>
       <c r="R42" t="n">
-        <v>7428036</v>
+        <v>7428040</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4988,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127375261</v>
+        <v>127375289</v>
       </c>
       <c r="B46" t="n">
-        <v>80161</v>
+        <v>91613</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>859630</v>
+        <v>859348</v>
       </c>
       <c r="R46" t="n">
-        <v>7428024</v>
+        <v>7428673</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5085,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127375289</v>
+        <v>127375261</v>
       </c>
       <c r="B47" t="n">
-        <v>91613</v>
+        <v>80161</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>859348</v>
+        <v>859630</v>
       </c>
       <c r="R47" t="n">
-        <v>7428673</v>
+        <v>7428024</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5182,32 +5182,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127375265</v>
+        <v>127375274</v>
       </c>
       <c r="B48" t="n">
-        <v>97353</v>
+        <v>92835</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>859346</v>
+        <v>859351</v>
       </c>
       <c r="R48" t="n">
-        <v>7428458</v>
+        <v>7428675</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5279,32 +5279,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127375274</v>
+        <v>127375265</v>
       </c>
       <c r="B49" t="n">
-        <v>92835</v>
+        <v>97353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>859351</v>
+        <v>859346</v>
       </c>
       <c r="R49" t="n">
-        <v>7428675</v>
+        <v>7428458</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>127331295</v>
       </c>
       <c r="B26" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>127331295</v>
       </c>
       <c r="B26" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120912441</v>
+        <v>127331338</v>
       </c>
       <c r="B2" t="n">
-        <v>106178</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>700 m NO om södra spetsen av Kaartiskajärvi, Nb</t>
+          <t>Kutkuavaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>859332</v>
+        <v>859704</v>
       </c>
       <c r="R2" t="n">
-        <v>7428537</v>
+        <v>7428407</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-08-02</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Norrbottens flora - 2010.</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,57 +756,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>frisk barrskogssluttning</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lennart Persson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Norrbottens flora 2010</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127331299</v>
+        <v>127331300</v>
       </c>
       <c r="B3" t="n">
-        <v>97353</v>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>859477</v>
+        <v>859702</v>
       </c>
       <c r="R3" t="n">
-        <v>7428516</v>
+        <v>7428406</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -883,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127331330</v>
+        <v>127331325</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -918,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>859645</v>
+        <v>859461</v>
       </c>
       <c r="R4" t="n">
-        <v>7428182</v>
+        <v>7427993</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,11 +969,11 @@
         <v>127331326</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1077,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127331288</v>
+        <v>127331330</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1112,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>859434</v>
+        <v>859645</v>
       </c>
       <c r="R6" t="n">
-        <v>7428190</v>
+        <v>7428182</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1177,11 +1163,11 @@
         <v>127331334</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1271,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127331300</v>
+        <v>127331335</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>859702</v>
+        <v>859493</v>
       </c>
       <c r="R8" t="n">
-        <v>7428406</v>
+        <v>7427919</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1368,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127331335</v>
+        <v>127375285</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1403,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>859493</v>
+        <v>859426</v>
       </c>
       <c r="R9" t="n">
-        <v>7427919</v>
+        <v>7428654</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1433,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1465,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127331338</v>
+        <v>127375286</v>
       </c>
       <c r="B10" t="n">
-        <v>78696</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>859704</v>
+        <v>859748</v>
       </c>
       <c r="R10" t="n">
-        <v>7428407</v>
+        <v>7428036</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1530,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1562,14 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127331325</v>
+        <v>127375288</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1597,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>859461</v>
+        <v>859567</v>
       </c>
       <c r="R11" t="n">
-        <v>7427993</v>
+        <v>7427909</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1627,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1662,7 +1648,7 @@
         <v>127331305</v>
       </c>
       <c r="B12" t="n">
-        <v>78787</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127375288</v>
+        <v>127331288</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1767,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1791,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>859567</v>
+        <v>859434</v>
       </c>
       <c r="R13" t="n">
-        <v>7427909</v>
+        <v>7428190</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1821,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1853,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127375293</v>
+        <v>127375262</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>80336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1864,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1888,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>859492</v>
+        <v>859390</v>
       </c>
       <c r="R14" t="n">
-        <v>7427913</v>
+        <v>7428241</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1924,11 +1910,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1955,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127375262</v>
+        <v>127375292</v>
       </c>
       <c r="B15" t="n">
-        <v>80036</v>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>859390</v>
+        <v>859490</v>
       </c>
       <c r="R15" t="n">
-        <v>7428241</v>
+        <v>7427925</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2026,6 +2007,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2052,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127375259</v>
+        <v>127375293</v>
       </c>
       <c r="B16" t="n">
-        <v>57832</v>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>859540</v>
+        <v>859492</v>
       </c>
       <c r="R16" t="n">
-        <v>7427886</v>
+        <v>7427913</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2123,6 +2109,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2149,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127375292</v>
+        <v>127331297</v>
       </c>
       <c r="B17" t="n">
-        <v>5177</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>859490</v>
+        <v>859721</v>
       </c>
       <c r="R17" t="n">
-        <v>7427925</v>
+        <v>7428024</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,17 +2205,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2254,7 +2240,7 @@
         <v>127375257</v>
       </c>
       <c r="B18" t="n">
-        <v>57832</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2351,7 +2337,7 @@
         <v>127375258</v>
       </c>
       <c r="B19" t="n">
-        <v>57832</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,32 +2431,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127375265</v>
+        <v>127375259</v>
       </c>
       <c r="B20" t="n">
-        <v>97353</v>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>859346</v>
+        <v>859540</v>
       </c>
       <c r="R20" t="n">
-        <v>7428458</v>
+        <v>7427886</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2539,6 +2525,588 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127331337</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>859496</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7428035</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127331299</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>859477</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7428516</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127375265</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>859346</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7428458</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127375268</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>859271</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7428513</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127375269</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>859378</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7428630</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127331294</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kutkuavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>859495</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7428024</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16008-2024 artfynd.xlsx
+++ b/artfynd/A 16008-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331338</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331300</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331325</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331326</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331330</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331334</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331335</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375285</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375286</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375288</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331305</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331288</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375262</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375292</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375293</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331297</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375257</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375258</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375259</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331337</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331299</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375265</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375268</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375269</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,8 +3232,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331294</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>